--- a/projects/dar-cairo-room-naming/Rooms_with_Equipment.xlsx
+++ b/projects/dar-cairo-room-naming/Rooms_with_Equipment.xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SSC'!$A$1:$J$86</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'HQ'!$A$1:$J$611</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'QNL'!$A$1:$J$198</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'QNL'!$A$1:$J$196</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -32562,7 +32562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J198"/>
+  <dimension ref="A1:J196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -32702,7 +32702,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -32711,11 +32711,11 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>VAV_B_S11_003, VAV_B_S11_004, VAV_B_S11_005, VAV_B_S11_006, VAV_B_S11_007, VAV_B_S11_008, VAV_B_S11_009, VAV_B_S11_010, VAV_B_S11_013, VAV_B_S11_014, VAV_B_S11_015, VAV_B_S11_016, VAV_B_S11_017, VAV_B_S11_018, VAV_B_S11_019, VAV_B_S11_020</t>
+          <t>VAV_B_S11_003, VAV_B_S11_004, VAV_B_S11_005, VAV_B_S11_006, VAV_B_S11_007, VAV_B_S11_008, VAV_B_S11_009, VAV_B_S11_010, VAV_B_S11_013, VAV_B_S11_014, VAV_B_S11_015, VAV_B_S11_016, VAV_B_S11_017, VAV_B_S11_018, VAV_B_S11_019, VAV_B_S11_020, VAV_B_S11_021</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -33070,7 +33070,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -33079,11 +33079,11 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>VAV_B_S11_021, VAV_B_S11_022, VAV_B_S11_023</t>
+          <t>VAV_B_S11_022, VAV_B_S11_023</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -33668,23 +33668,23 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>CAV</t>
+          <t>CAV, DX Unit</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>CAV_B_S13_006, CAV_B_S13_007, CAV_B_S13_008</t>
+          <t>CAV_B_S13_006, CAV_B_S13_007, CAV_B_S13_008, DX_B01, DX_B02</t>
         </is>
       </c>
       <c r="I24" t="n">
         <v>3</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -34450,23 +34450,23 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>CAV</t>
+          <t>CAV, EF</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>CAV_B_S13_001, CAV_B_S13_002, CAV_B_S13_003, CAV_B_S13_004, CAV_B_S13_005, CAV_B_S13_014</t>
+          <t>CAV_B_S13_001, CAV_B_S13_002, CAV_B_S13_003, CAV_B_S13_004, CAV_B_S13_005, CAV_B_S13_014, EF_B14</t>
         </is>
       </c>
       <c r="I41" t="n">
         <v>6</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -34542,23 +34542,23 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>FCU, EF</t>
+          <t>FCU</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>EF_B14, FCU_B_006</t>
+          <t>FCU_B_006</t>
         </is>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -34661,12 +34661,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>entity:QNL_B-081_Corridor-4</t>
+          <t>entity:QNL_B-082_Transformer-Room</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>B.081 CORRIDOR 4</t>
+          <t>B.082 TRANSFORMER ROOM</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -34676,11 +34676,11 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>B.081</t>
+          <t>B.082</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -34689,14 +34689,14 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>DX_B01, DX_B02</t>
+          <t>DX_B04</t>
         </is>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -34707,12 +34707,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>entity:QNL_B-082_Transformer-Room</t>
+          <t>entity:QNL_B-083_HV-Room</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>B.082 TRANSFORMER ROOM</t>
+          <t>B.083 HV ROOM</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -34722,11 +34722,11 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>B.082</t>
+          <t>B.083</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -34735,14 +34735,14 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>DX_B03, DX_B04, DX_B14</t>
+          <t>DX_B05, DX_B06</t>
         </is>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -34753,12 +34753,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>entity:QNL_B-083_HV-Room</t>
+          <t>entity:QNL_B-084_UPS-Battery-Room</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>B.083 HV ROOM</t>
+          <t>B.084 UPS BATTERY ROOM</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -34768,7 +34768,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>B.083</t>
+          <t>B.084</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -34776,12 +34776,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>DX Unit</t>
+          <t>CAV, DX Unit</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>DX_B05, DX_B06</t>
+          <t>CAV_B_S13_020, DX_B09</t>
         </is>
       </c>
       <c r="I48" t="n">
@@ -34799,12 +34799,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>entity:QNL_B-084_UPS-Battery-Room</t>
+          <t>entity:QNL_B-085_Fumigation-Room</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>B.084 UPS BATTERY ROOM</t>
+          <t>B.085 FUMIGATION ROOM</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -34814,7 +34814,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>B.084</t>
+          <t>B.085</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -34822,19 +34822,19 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>CAV, DX Unit</t>
+          <t>FCU, VAV, EF</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>CAV_B_S13_020, DX_B08, DX_B09</t>
+          <t>EF_B05, FCU_B_002, VAV_B_S13_006</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -34845,12 +34845,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>entity:QNL_B-085_Fumigation-Room</t>
+          <t>entity:QNL_B-087_Gas-Suppression-Room</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>B.085 FUMIGATION ROOM</t>
+          <t>B.087 GAS SUPPRESSION ROOM</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -34860,27 +34860,27 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>B.085</t>
+          <t>B.087</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>FCU, VAV, EF</t>
+          <t>FCU, CAV</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>EF_B05, FCU_B_002, VAV_B_S13_006</t>
+          <t>CAV_B_S13_013, FCU_B_008</t>
         </is>
       </c>
       <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
         <v>2</v>
-      </c>
-      <c r="J50" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -34891,12 +34891,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>entity:QNL_B-087_Gas-Suppression-Room</t>
+          <t>entity:QNL_B-088_People-Mover-Plant</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>B.087 GAS SUPPRESSION ROOM</t>
+          <t>B.088 PEOPLE MOVER PLANT</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -34906,27 +34906,27 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>B.087</t>
+          <t>B.088</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>FCU, CAV</t>
+          <t>FCU</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>CAV_B_S13_013, FCU_B_008</t>
+          <t>FCU_B_009</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -34937,12 +34937,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>entity:QNL_B-088_People-Mover-Plant</t>
+          <t>entity:QNL_B-089_Server-Room</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>B.088 PEOPLE MOVER PLANT</t>
+          <t>B.089 SERVER ROOM</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -34952,27 +34952,27 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>B.088</t>
+          <t>B.089</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>FCU</t>
+          <t>CAV, CCU</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>FCU_B_009</t>
+          <t>CAV_B_S13_015, CCU_B05, CCU_B06, CCU_B07</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
@@ -34983,12 +34983,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>entity:QNL_B-089_Server-Room</t>
+          <t>entity:QNL_B-091_Fuel-Room</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>B.089 SERVER ROOM</t>
+          <t>B.091 FUEL ROOM</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -34998,27 +34998,27 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>B.089</t>
+          <t>B.091</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>CAV, CCU</t>
+          <t>EF</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>CAV_B_S13_015, CCU_B05, CCU_B06, CCU_B07</t>
+          <t>EF_B11</t>
         </is>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -35029,12 +35029,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>entity:QNL_B-091_Fuel-Room</t>
+          <t>entity:QNL_B-092_Storage</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>B.091 FUEL ROOM</t>
+          <t>B.092 STORAGE</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -35044,7 +35044,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>B.091</t>
+          <t>B.092</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -35052,12 +35052,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>EF</t>
+          <t>DX Unit</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>EF_B11</t>
+          <t>DX_B20</t>
         </is>
       </c>
       <c r="I54" t="n">
@@ -35075,12 +35075,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>entity:QNL_B-092_Storage</t>
+          <t>entity:QNL_B-093_Transh-Chamber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>B.092 STORAGE</t>
+          <t>B.093 TRANSH CHAMBER</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -35090,27 +35090,27 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>B.092</t>
+          <t>B.093</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>DX Unit</t>
+          <t>DX Unit, EF</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>DX_B20</t>
+          <t>DX_B13, DX_B15, EF_B10</t>
         </is>
       </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -35121,12 +35121,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>entity:QNL_B-093_Transh-Chamber</t>
+          <t>entity:QNL_B-095_Emergency-Lighting-Battery-Room</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>B.093 TRANSH CHAMBER</t>
+          <t>B.095 EMERGENCY LIGHTING BATTERY ROOM</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -35136,27 +35136,27 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>B.093</t>
+          <t>B.095</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>DX Unit, EF</t>
+          <t>DX Unit</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>DX_B13, DX_B15, EF_B10</t>
+          <t>DX_B03, DX_B07, DX_B08, DX_B14, DX_B16</t>
         </is>
       </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57">
@@ -35167,12 +35167,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>entity:QNL_B-095_Emergency-Lighting-Battery-Room</t>
+          <t>entity:QNL_B-101_Shipping-Clirk</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>B.095 EMERGENCY LIGHTING BATTERY ROOM</t>
+          <t>B.101 SHIPPING CLIRK</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -35182,27 +35182,27 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>B.095</t>
+          <t>B.101</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>DX Unit</t>
+          <t>VAV</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>DX_B07, DX_B16</t>
+          <t>VAV_B_S13_007</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -35213,12 +35213,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>entity:QNL_B-101_Shipping-Clirk</t>
+          <t>entity:QNL_B-103_Processing-Room</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>B.101 SHIPPING CLIRK</t>
+          <t>B.103 PROCESSING ROOM</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -35228,27 +35228,27 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>B.101</t>
+          <t>B.103</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>VAV</t>
+          <t>VAV, DX Unit</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>VAV_B_S13_007</t>
+          <t>DX_B10, VAV_B_S13_003, VAV_B_S13_004</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -35259,12 +35259,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>entity:QNL_B-102_Processing-Rm</t>
+          <t>entity:QNL_B-104A_Plant-Room</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>B.102 PROCESSING RM</t>
+          <t>B.104A PLANT ROOM</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -35274,7 +35274,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>B.102</t>
+          <t>B.104A</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -35282,12 +35282,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>DX Unit</t>
+          <t>CAV</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>DX_B10</t>
+          <t>CAV_B_S13_050</t>
         </is>
       </c>
       <c r="I59" t="n">
@@ -35305,12 +35305,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>entity:QNL_B-103_Processing-Room</t>
+          <t>entity:QNL_B-104_Storage</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>B.103 PROCESSING ROOM</t>
+          <t>B.104 STORAGE</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -35320,24 +35320,24 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>B.103</t>
+          <t>B.104</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>VAV</t>
+          <t>CAV</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>VAV_B_S13_003, VAV_B_S13_004</t>
+          <t>CAV_B_S13_009</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -35351,12 +35351,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>entity:QNL_B-104A_Plant-Room</t>
+          <t>entity:QNL_B-105_Security-Contol-Room</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>B.104A PLANT ROOM</t>
+          <t>B.105 SECURITY CONTOL ROOM</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -35366,27 +35366,27 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>B.104A</t>
+          <t>B.105</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>CAV</t>
+          <t>FCU, VAV</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>CAV_B_S13_050</t>
+          <t>FCU_B_010, VAV_B_S13_008</t>
         </is>
       </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -35397,12 +35397,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>entity:QNL_B-104_Storage</t>
+          <t>entity:QNL_B-106_Rest-Room-Security</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>B.104 STORAGE</t>
+          <t>B.106 REST ROOM SECURITY</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -35412,7 +35412,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>B.104</t>
+          <t>B.106</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -35420,19 +35420,19 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>CAV</t>
+          <t>DX Unit</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>CAV_B_S13_009</t>
+          <t>DX_B22</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -35443,12 +35443,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>entity:QNL_B-105_Security-Contol-Room</t>
+          <t>entity:QNL_B-107_Security-Equipment-Room</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>B.105 SECURITY CONTOL ROOM</t>
+          <t>B.107 SECURITY EQUIPMENT ROOM</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -35458,27 +35458,27 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>B.105</t>
+          <t>B.107</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>FCU, VAV</t>
+          <t>DX Unit</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>FCU_B_010, VAV_B_S13_008</t>
+          <t>DX_B11, DX_B12, DX_B23</t>
         </is>
       </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
@@ -35489,12 +35489,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>entity:QNL_B-106_Rest-Room-Security</t>
+          <t>entity:QNL_B-109_Loading-Area</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>B.106 REST ROOM SECURITY</t>
+          <t>B.109 LOADING AREA</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -35504,27 +35504,27 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>B.106</t>
+          <t>B.109</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>DX Unit</t>
+          <t>EF</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>DX_B22</t>
+          <t>EF_B07, EF_B08, EF_B15, EF_B16</t>
         </is>
       </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
@@ -35535,12 +35535,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>entity:QNL_B-107_Security-Equipment-Room</t>
+          <t>entity:QNL_B-110_Plant-Room-03</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>B.107 SECURITY EQUIPMENT ROOM</t>
+          <t>B.110 PLANT ROOM 03</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -35550,27 +35550,27 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>B.107</t>
+          <t>B.110</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>DX Unit</t>
+          <t>AHU, FCU, CAV, TEF</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>DX_B11, DX_B12, DX_B23</t>
+          <t>AHUB004, AHUB009, AHUB014, AHUB015, CAV_B_S14_003, CAV_B_S14_004, CAV_B_S14_005, FCU_B_015, FCU_B_016, FCU_B_017, TEF_B01A, TEF_B01B</t>
         </is>
       </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="66">
@@ -35581,12 +35581,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>entity:QNL_B-109_Loading-Area</t>
+          <t>entity:QNL_B-120_Compact-Shelving-Main-Collection</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>B.109 LOADING AREA</t>
+          <t>B.120 COMPACT SHELVING MAIN COLLECTION</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -35596,27 +35596,27 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>B.109</t>
+          <t>B.120</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>EF</t>
+          <t>TEF</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>EF_B07, EF_B08, EF_B15, EF_B16</t>
+          <t>TEF_B03A, TEF_B03B</t>
         </is>
       </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -35627,12 +35627,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>entity:QNL_B-110_Plant-Room-03</t>
+          <t>entity:QNL_B-121_Sorting-Shelving-Room</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>B.110 PLANT ROOM 03</t>
+          <t>B.121 SORTING SHELVING ROOM</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -35642,27 +35642,27 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>B.110</t>
+          <t>B.121</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>AHU, FCU, CAV, TEF</t>
+          <t>FCU</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>AHUB004, AHUB009, AHUB014, AHUB015, CAV_B_S14_003, CAV_B_S14_004, CAV_B_S14_005, FCU_B_015, FCU_B_016, FCU_B_017, TEF_B01A, TEF_B01B</t>
+          <t>FCU_B_027, FCU_B_028</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J67" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -35673,12 +35673,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>entity:QNL_B-120_Compact-Shelving-Main-Collection</t>
+          <t>entity:QNL_B-122_IT-Office</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>B.120 COMPACT SHELVING MAIN COLLECTION</t>
+          <t>B.122 IT OFFICE</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -35688,27 +35688,27 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>B.120</t>
+          <t>B.122</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>TEF</t>
+          <t>FCU</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>TEF_B03A, TEF_B03B</t>
+          <t>FCU_B_036</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -35719,12 +35719,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>entity:QNL_B-121_Sorting-Shelving-Room</t>
+          <t>entity:QNL_B-132_Shell-Space-Special-Collection</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>B.121 SORTING SHELVING ROOM</t>
+          <t>B.132 SHELL SPACE SPECIAL COLLECTION</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -35734,11 +35734,11 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>B.121</t>
+          <t>B.132</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -35747,11 +35747,11 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>FCU_B_027, FCU_B_028</t>
+          <t>FCU_B_032, FCU_B_033, FCU_B_034, FCU_B_035</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -35765,12 +35765,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>entity:QNL_B-122_IT-Office</t>
+          <t>entity:QNL_B-140_Hl-Plant-Room</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>B.122 IT OFFICE</t>
+          <t>B.140 HL PLANT ROOM</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -35780,7 +35780,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>B.122</t>
+          <t>B.140</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -35793,14 +35793,14 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>FCU_B_036</t>
+          <t>FCU_B_005</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -35811,12 +35811,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>entity:QNL_B-132_Shell-Space-Special-Collection</t>
+          <t>entity:QNL_B-141_Vault</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>B.132 SHELL SPACE SPECIAL COLLECTION</t>
+          <t>B.141 VAULT</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -35826,27 +35826,27 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>B.132</t>
+          <t>B.141</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>FCU</t>
+          <t>CCU</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>FCU_B_032, FCU_B_033, FCU_B_034, FCU_B_035</t>
+          <t>CCU_B08, CCU_B09</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -35857,12 +35857,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>entity:QNL_B-140_Hl-Plant-Room</t>
+          <t>entity:QNL_B-145_Loby-And-Csecurity</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>B.140 HL PLANT ROOM</t>
+          <t>B.145 LOBY AND CSECURITY</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -35872,27 +35872,27 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>B.140</t>
+          <t>B.145</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>FCU</t>
+          <t>FCU, VAV</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>FCU_B_005</t>
+          <t>FCU_B_029, FCU_B_038, VAV_B_S15_002, VAV_B_S15_003, VAV_B_S15_004</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73">
@@ -35903,12 +35903,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>entity:QNL_B-141_Vault</t>
+          <t>entity:QNL_B-149_HC-Director-Head</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>B.141 VAULT</t>
+          <t>B.149 HC DIRECTOR HEAD</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -35918,27 +35918,27 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>B.141</t>
+          <t>B.149</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>CCU</t>
+          <t>VAV</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>CCU_B08, CCU_B09</t>
+          <t>VAV_B_S15_009, VAV_B_S15_010, VAV_B_S15_011, VAV_B_S15_012</t>
         </is>
       </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
@@ -35949,12 +35949,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>entity:QNL_B-145_Loby-And-Csecurity</t>
+          <t>entity:QNL_B-151_Research-And-Doc-Record-Mgmt</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>B.145 LOBY AND CSECURITY</t>
+          <t>B.151 RESEARCH AND DOC RECORD MGMT</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -35964,27 +35964,27 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>B.145</t>
+          <t>B.151</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>FCU, VAV</t>
+          <t>VAV</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>FCU_B_029, FCU_B_038, VAV_B_S15_002, VAV_B_S15_003, VAV_B_S15_004</t>
+          <t>VAV_B_S15_008, VAV_B_S15_013</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J74" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -35995,12 +35995,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>entity:QNL_B-149_HC-Director-Head</t>
+          <t>entity:QNL_B-152_HC-Security-Room</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>B.149 HC DIRECTOR HEAD</t>
+          <t>B.152 HC SECURITY ROOM</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -36010,11 +36010,11 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>B.149</t>
+          <t>B.152</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -36023,14 +36023,14 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>VAV_B_S15_009, VAV_B_S15_010, VAV_B_S15_011, VAV_B_S15_012</t>
+          <t>VAV_B_S15_007</t>
         </is>
       </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -36041,12 +36041,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>entity:QNL_B-151_Research-And-Doc-Record-Mgmt</t>
+          <t>entity:QNL_B-153_Prof-Librarian</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>B.151 RESEARCH AND DOC RECORD MGMT</t>
+          <t>B.153 PROF LIBRARIAN</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -36056,11 +36056,11 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>B.151</t>
+          <t>B.153</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -36069,11 +36069,11 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>VAV_B_S15_008, VAV_B_S15_013</t>
+          <t>VAV_B_S15_001, VAV_B_S15_005, VAV_B_S15_006</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -36087,12 +36087,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>entity:QNL_B-152_HC-Security-Room</t>
+          <t>entity:QNL_B-155_Faculty-Carrels</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>B.152 HC SECURITY ROOM</t>
+          <t>B.155 FACULTY CARRELS</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -36102,7 +36102,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>B.152</t>
+          <t>B.155</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -36110,12 +36110,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>VAV</t>
+          <t>FCU</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>VAV_B_S15_007</t>
+          <t>FCU_B_001</t>
         </is>
       </c>
       <c r="I77" t="n">
@@ -36133,12 +36133,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>entity:QNL_B-153_Prof-Librarian</t>
+          <t>entity:QNL_B-200_Digitization</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>B.153 PROF LIBRARIAN</t>
+          <t>B.200 DIGITIZATION</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -36148,11 +36148,11 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>B.153</t>
+          <t>B.200</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -36161,11 +36161,11 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>VAV_B_S15_001, VAV_B_S15_005, VAV_B_S15_006</t>
+          <t>VAV_B_S10_001, VAV_B_S10_002, VAV_B_S10_003, VAV_B_S10_004, VAV_B_S10_005, VAV_B_S10_006, VAV_B_S10_007, VAV_B_S10_008, VAV_B_S10_024</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -36179,12 +36179,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>entity:QNL_B-155_Faculty-Carrels</t>
+          <t>entity:QNL_B-203_Technical-Services</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>B.155 FACULTY CARRELS</t>
+          <t>B.203 TECHNICAL SERVICES</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -36194,7 +36194,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>B.155</t>
+          <t>B.203</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -36202,19 +36202,19 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>FCU</t>
+          <t>VAV</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>FCU_B_001</t>
+          <t>VAV_B_S10_009</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -36225,12 +36225,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>entity:QNL_B-200_Digitization</t>
+          <t>entity:QNL_B-204_Technical-Services</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>B.200 DIGITIZATION</t>
+          <t>B.204 TECHNICAL SERVICES</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -36240,11 +36240,11 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>B.200</t>
+          <t>B.204</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -36253,11 +36253,11 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>VAV_B_S10_001, VAV_B_S10_002, VAV_B_S10_003, VAV_B_S10_004, VAV_B_S10_005, VAV_B_S10_006, VAV_B_S10_007, VAV_B_S10_008, VAV_B_S10_024</t>
+          <t>VAV_B_S10_010, VAV_B_S10_011</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -36271,12 +36271,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>entity:QNL_B-203_Technical-Services</t>
+          <t>entity:QNL_B-205_Instruction-Presentation</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>B.203 TECHNICAL SERVICES</t>
+          <t>B.205 INSTRUCTION PRESENTATION</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -36286,11 +36286,11 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>B.203</t>
+          <t>B.205</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -36299,11 +36299,11 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>VAV_B_S10_009</t>
+          <t>VAV_B_S10_016, VAV_B_S10_017, VAV_B_S10_018</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -36317,12 +36317,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>entity:QNL_B-204_Technical-Services</t>
+          <t>entity:QNL_B-206_Instruction-Outreach</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>B.204 TECHNICAL SERVICES</t>
+          <t>B.206 INSTRUCTION OUTREACH</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -36332,11 +36332,11 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>B.204</t>
+          <t>B.206</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -36345,11 +36345,11 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>VAV_B_S10_010, VAV_B_S10_011</t>
+          <t>VAV_B_S10_015</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -36363,12 +36363,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>entity:QNL_B-205_Instruction-Presentation</t>
+          <t>entity:QNL_B-207_Reserchers-Reading-Area</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>B.205 INSTRUCTION PRESENTATION</t>
+          <t>B.207 RESERCHERS READING AREA</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -36378,11 +36378,11 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>B.205</t>
+          <t>B.207</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -36391,11 +36391,11 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>VAV_B_S10_016, VAV_B_S10_017, VAV_B_S10_018</t>
+          <t>VAV_B_S10_020, VAV_B_S10_021, VAV_B_S10_022, VAV_B_S10_023</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -36409,12 +36409,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>entity:QNL_B-206_Instruction-Outreach</t>
+          <t>entity:QNL_B-208_Prof-Librarian</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>B.206 INSTRUCTION OUTREACH</t>
+          <t>B.208 PROF LIBRARIAN</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -36424,7 +36424,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>B.206</t>
+          <t>B.208</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -36437,7 +36437,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>VAV_B_S10_015</t>
+          <t>VAV_B_S10_019</t>
         </is>
       </c>
       <c r="I84" t="n">
@@ -36455,12 +36455,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>entity:QNL_B-207_Reserchers-Reading-Area</t>
+          <t>entity:QNL_B-209_Conservation-Work-Area</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>B.207 RESERCHERS READING AREA</t>
+          <t>B.209 CONSERVATION WORK AREA</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -36470,11 +36470,11 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>B.207</t>
+          <t>B.209</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -36483,11 +36483,11 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>VAV_B_S10_020, VAV_B_S10_021, VAV_B_S10_022, VAV_B_S10_023</t>
+          <t>VAV_B_S10_012, VAV_B_S10_013, VAV_B_S10_014</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -36501,12 +36501,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>entity:QNL_B-208_Prof-Librarian</t>
+          <t>entity:QNL_B-210_FM-Storage</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>B.208 PROF LIBRARIAN</t>
+          <t>B.210 FM STORAGE</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -36516,24 +36516,24 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>B.208</t>
+          <t>B.210</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>VAV</t>
+          <t>FCU</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>VAV_B_S10_019</t>
+          <t>FCU_B_022, FCU_B_023</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -36547,12 +36547,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>entity:QNL_B-209_Conservation-Work-Area</t>
+          <t>entity:QNL_B-211_Ph-Plant-Room</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>B.209 CONSERVATION WORK AREA</t>
+          <t>B.211 PH PLANT ROOM</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -36562,27 +36562,27 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>B.209</t>
+          <t>B.211</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>VAV</t>
+          <t>FCU, HEX</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>VAV_B_S10_012, VAV_B_S10_013, VAV_B_S10_014</t>
+          <t>FCU_B_024, HEX05</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
@@ -36593,12 +36593,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>entity:QNL_B-210_FM-Storage</t>
+          <t>entity:QNL_B-212_Misting-Pump-Room</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>B.210 FM STORAGE</t>
+          <t>B.212 MISTING PUMP ROOM</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -36608,7 +36608,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>B.210</t>
+          <t>B.212</t>
         </is>
       </c>
       <c r="F88" t="n">
@@ -36621,14 +36621,14 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>FCU_B_022, FCU_B_023</t>
+          <t>FCU_B_025, FCU_B_026</t>
         </is>
       </c>
       <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="n">
         <v>2</v>
-      </c>
-      <c r="J88" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -36639,12 +36639,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>entity:QNL_B-211_Ph-Plant-Room</t>
+          <t>entity:QNL_B-214_IDF-Room</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>B.211 PH PLANT ROOM</t>
+          <t>B.214 IDF ROOM</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -36654,27 +36654,27 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>B.211</t>
+          <t>B.214</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>FCU, HEX</t>
+          <t>EF</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>FCU_B_024, HEX05</t>
+          <t>EF_B12</t>
         </is>
       </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -36685,12 +36685,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>entity:QNL_B-212_Misting-Pump-Room</t>
+          <t>entity:QNL_B-215A_IDF</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>B.212 MISTING PUMP ROOM</t>
+          <t>B.215A IDF</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -36700,7 +36700,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>B.212</t>
+          <t>B.215A</t>
         </is>
       </c>
       <c r="F90" t="n">
@@ -36713,7 +36713,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>FCU_B_025, FCU_B_026</t>
+          <t>FCU_B_031, FCU_B_037</t>
         </is>
       </c>
       <c r="I90" t="n">
@@ -36731,12 +36731,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>entity:QNL_B-214_IDF-Room</t>
+          <t>entity:QNL_B-215_IDF-FM-Storage</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>B.214 IDF ROOM</t>
+          <t>B.215 IDF FM STORAGE</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -36746,7 +36746,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>B.214</t>
+          <t>B.215</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -36754,12 +36754,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>EF</t>
+          <t>FCU</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>EF_B12</t>
+          <t>FCU_B_004</t>
         </is>
       </c>
       <c r="I91" t="n">
@@ -36777,12 +36777,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>entity:QNL_B-215A_IDF</t>
+          <t>entity:QNL_B-220_Plant-Room-04</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>B.215A IDF</t>
+          <t>B.220 PLANT ROOM 04</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -36792,27 +36792,27 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>B.215A</t>
+          <t>B.220</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>FCU</t>
+          <t>AHU, FCU, HEX, CHW Pump</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>FCU_B_031, FCU_B_037</t>
+          <t>AHUB001, AHUB005, AHUB006, AHUB007, AHUB008, CHWPU_P01, CHW_P01, CHW_P02, CHW_P03, CHW_P04, FCU_B_018, FCU_B_019, FCU_B_020, FCU_B_021, HEX01, HEX02, HEX03, HEX04</t>
         </is>
       </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="93">
@@ -36823,12 +36823,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>entity:QNL_B-215_IDF-FM-Storage</t>
+          <t>entity:QNL_B-222_IDF</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>B.215 IDF FM STORAGE</t>
+          <t>B.222 IDF</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -36838,27 +36838,27 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>B.215</t>
+          <t>B.222</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>FCU</t>
+          <t>CCU</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>FCU_B_004</t>
+          <t>CCU_B10, CCU_B11</t>
         </is>
       </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
@@ -36869,12 +36869,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>entity:QNL_B-220_Plant-Room-04</t>
+          <t>entity:QNL_B-226_Pump-Rm-4</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>B.220 PLANT ROOM 04</t>
+          <t>B.226 PUMP RM 4</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -36884,27 +36884,27 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>B.220</t>
+          <t>B.226</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>AHU, FCU, HEX, CHW Pump</t>
+          <t>FCU</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>AHUB001, AHUB005, AHUB006, AHUB007, AHUB008, CHWPU_P01, CHW_P01, CHW_P02, CHW_P03, CHW_P04, FCU_B_018, FCU_B_019, FCU_B_020, FCU_B_021, HEX01, HEX02, HEX03, HEX04</t>
+          <t>FCU_B_030</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -36915,42 +36915,42 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>entity:QNL_B-222_IDF</t>
+          <t>entity:QNL_L1-001_Open-Reading-Area</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>B.222 IDF</t>
+          <t>L1.001 OPEN READING AREA</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>B.222</t>
+          <t>L1.001</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>CCU</t>
+          <t>VAV</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>CCU_B10, CCU_B11</t>
+          <t>VAV_2F_S12_001, VAV_2F_S12_002, VAV_2F_S12_003, VAV_2F_S12_004, VAV_2F_S12_005, VAV_2F_S12_006, VAV_2F_S12_007, VAV_2F_S12_008, VAV_2F_S12_009</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -36961,39 +36961,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>entity:QNL_B-226_Pump-Rm-4</t>
+          <t>entity:QNL_L1-002A_Greem-Room</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>B.226 PUMP RM 4</t>
+          <t>L1.002A GREEM ROOM</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>B.226</t>
+          <t>L1.002A</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>FCU</t>
+          <t>VAV</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>FCU_B_030</t>
+          <t>VAV_1F_S15_039, VAV_1F_S15_040</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -37007,12 +37007,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-001_Open-Reading-Area</t>
+          <t>entity:QNL_L1-002_Braille-Reader</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>L1.001 OPEN READING AREA</t>
+          <t>L1.002 BRAILLE READER</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -37022,11 +37022,11 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>L1.001</t>
+          <t>L1.002</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -37035,11 +37035,11 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>VAV_2F_S12_001, VAV_2F_S12_002, VAV_2F_S12_003, VAV_2F_S12_004, VAV_2F_S12_005, VAV_2F_S12_006, VAV_2F_S12_007, VAV_2F_S12_008, VAV_2F_S12_009</t>
+          <t>VAV_2F_S12_010, VAV_2F_S12_011</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -37053,12 +37053,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-002A_Greem-Room</t>
+          <t>entity:QNL_L1-003_Tutoring-Head</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>L1.002A GREEM ROOM</t>
+          <t>L1.003 TUTORING HEAD</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -37068,11 +37068,11 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>L1.002A</t>
+          <t>L1.003</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -37081,11 +37081,11 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>VAV_1F_S15_039, VAV_1F_S15_040</t>
+          <t>VAV_2F_S12_012</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -37099,12 +37099,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-002_Braille-Reader</t>
+          <t>entity:QNL_L1-004_Writing-Room-1</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>L1.002 BRAILLE READER</t>
+          <t>L1.004 WRITING ROOM 1</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -37114,11 +37114,11 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>L1.002</t>
+          <t>L1.004</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -37127,11 +37127,11 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>VAV_2F_S12_010, VAV_2F_S12_011</t>
+          <t>VAV_2F_S12_013</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -37145,12 +37145,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-003_Tutoring-Head</t>
+          <t>entity:QNL_L1-005_Writing-Room-2</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>L1.003 TUTORING HEAD</t>
+          <t>L1.005 WRITING ROOM 2</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -37160,11 +37160,11 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>L1.003</t>
+          <t>L1.005</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -37173,11 +37173,11 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>VAV_2F_S12_012</t>
+          <t>VAV_2F_S12_014, VAV_2F_S12_015</t>
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -37191,12 +37191,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-004_Writing-Room-1</t>
+          <t>entity:QNL_L1-007_Student-Carrels</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>L1.004 WRITING ROOM 1</t>
+          <t>L1.007 STUDENT CARRELS</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -37206,11 +37206,11 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>L1.004</t>
+          <t>L1.007</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -37219,11 +37219,11 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>VAV_2F_S12_013</t>
+          <t>VAV_2F_S12_016, VAV_2F_S12_017, VAV_2F_S12_018, VAV_2F_S12_019, VAV_2F_S12_020</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -37237,12 +37237,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-005_Writing-Room-2</t>
+          <t>entity:QNL_L1-020_Info-Literacy-Instr1</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>L1.005 WRITING ROOM 2</t>
+          <t>L1.020 INFO LITERACY INSTR1</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -37252,7 +37252,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>L1.005</t>
+          <t>L1.020</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -37265,7 +37265,7 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>VAV_2F_S12_014, VAV_2F_S12_015</t>
+          <t>VAV_1F_S11_004, VAV_1F_S11_005</t>
         </is>
       </c>
       <c r="I102" t="n">
@@ -37283,12 +37283,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-007_Student-Carrels</t>
+          <t>entity:QNL_L1-021_Infor-Lteracy-Instr-2</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>L1.007 STUDENT CARRELS</t>
+          <t>L1.021 INFOR LTERACY INSTR 2</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -37298,11 +37298,11 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>L1.007</t>
+          <t>L1.021</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -37311,11 +37311,11 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>VAV_2F_S12_016, VAV_2F_S12_017, VAV_2F_S12_018, VAV_2F_S12_019, VAV_2F_S12_020</t>
+          <t>VAV_1F_S11_006, VAV_1F_S11_007, VAV_1F_S11_008, VAV_1F_S11_009, VAV_1F_S11_010, VAV_1F_S11_011, VAV_1F_S11_012, VAV_1F_S11_013</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -37329,12 +37329,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-020_Info-Literacy-Instr1</t>
+          <t>entity:QNL_L1-022_Computer-Class-Rm</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>L1.020 INFO LITERACY INSTR1</t>
+          <t>L1.022 COMPUTER CLASS RM</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -37344,11 +37344,11 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>L1.020</t>
+          <t>L1.022</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -37357,11 +37357,11 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>VAV_1F_S11_004, VAV_1F_S11_005</t>
+          <t>VAV_1F_S11_014, VAV_1F_S11_015, VAV_1F_S11_016, VAV_1F_S11_017, VAV_1F_S11_018, VAV_1F_S11_019, VAV_1F_S11_020, VAV_1F_S11_021</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -37375,12 +37375,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-021_Infor-Lteracy-Instr-2</t>
+          <t>entity:QNL_L1-023_Corridor</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>L1.021 INFOR LTERACY INSTR 2</t>
+          <t>L1.023 CORRIDOR</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -37390,24 +37390,24 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>L1.021</t>
+          <t>L1.023</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>VAV</t>
+          <t>VAV, CAV</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>VAV_1F_S11_006, VAV_1F_S11_007, VAV_1F_S11_008, VAV_1F_S11_009, VAV_1F_S11_010, VAV_1F_S11_011, VAV_1F_S11_012, VAV_1F_S11_013</t>
+          <t>CAV_1F_S11_001, CAV_1F_S11_002, CAV_1F_S11_007, VAV_1F_S11_087, VAV_1F_S11_088, VAV_1F_S11_089, VAV_1F_S11_090</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -37421,12 +37421,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-022_Computer-Class-Rm</t>
+          <t>entity:QNL_L1-026_Group-Study-Room1</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>L1.022 COMPUTER CLASS RM</t>
+          <t>L1.026 GROUP STUDY ROOM1</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -37436,11 +37436,11 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>L1.022</t>
+          <t>L1.026</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -37449,11 +37449,11 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>VAV_1F_S11_014, VAV_1F_S11_015, VAV_1F_S11_016, VAV_1F_S11_017, VAV_1F_S11_018, VAV_1F_S11_019, VAV_1F_S11_020, VAV_1F_S11_021</t>
+          <t>VAV_1F_S11_001</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -37467,12 +37467,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-023_Corridor</t>
+          <t>entity:QNL_L1-027_Group-Study-Room2</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>L1.023 CORRIDOR</t>
+          <t>L1.027 GROUP STUDY ROOM2</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -37482,24 +37482,24 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>L1.023</t>
+          <t>L1.027</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>VAV, CAV</t>
+          <t>VAV</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>CAV_1F_S11_001, CAV_1F_S11_002, CAV_1F_S11_007, VAV_1F_S11_087, VAV_1F_S11_088, VAV_1F_S11_089, VAV_1F_S11_090</t>
+          <t>VAV_1F_S11_002</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -37513,12 +37513,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-026_Group-Study-Room1</t>
+          <t>entity:QNL_L1-028_Group-Study-Room3</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>L1.026 GROUP STUDY ROOM1</t>
+          <t>L1.028 GROUP STUDY ROOM3</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -37528,7 +37528,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>L1.026</t>
+          <t>L1.028</t>
         </is>
       </c>
       <c r="F108" t="n">
@@ -37541,7 +37541,7 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>VAV_1F_S11_001</t>
+          <t>VAV_1F_S11_003</t>
         </is>
       </c>
       <c r="I108" t="n">
@@ -37559,12 +37559,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-027_Group-Study-Room2</t>
+          <t>entity:QNL_L1-029_Group-Study-Room-4</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>L1.027 GROUP STUDY ROOM2</t>
+          <t>L1.029 GROUP STUDY ROOM 4</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -37574,7 +37574,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>L1.027</t>
+          <t>L1.029</t>
         </is>
       </c>
       <c r="F109" t="n">
@@ -37587,7 +37587,7 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>VAV_1F_S11_002</t>
+          <t>VAV_1F_S11_022</t>
         </is>
       </c>
       <c r="I109" t="n">
@@ -37605,12 +37605,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-028_Group-Study-Room3</t>
+          <t>entity:QNL_L1-030_ICT-Room-02</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>L1.028 GROUP STUDY ROOM3</t>
+          <t>L1.030 ICT ROOM 02</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -37620,7 +37620,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>L1.028</t>
+          <t>L1.030</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -37628,12 +37628,12 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>VAV</t>
+          <t>FCU</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>VAV_1F_S11_003</t>
+          <t>FCU_1F_002</t>
         </is>
       </c>
       <c r="I110" t="n">
@@ -37651,12 +37651,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-029_Group-Study-Room-4</t>
+          <t>entity:QNL_L1-040_Head-Librarian-Office</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>L1.029 GROUP STUDY ROOM 4</t>
+          <t>L1.040 HEAD LIBRARIAN OFFICE</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -37666,7 +37666,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>L1.029</t>
+          <t>L1.040</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -37679,14 +37679,14 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>VAV_1F_S11_022</t>
+          <t>VAV_1F_S15_005</t>
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -37697,12 +37697,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-030_ICT-Room-02</t>
+          <t>entity:QNL_L1-041_Multipurpose-Room</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>L1.030 ICT ROOM 02</t>
+          <t>L1.041 MULTIPURPOSE ROOM</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -37712,24 +37712,24 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>L1.030</t>
+          <t>L1.041</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>FCU</t>
+          <t>VAV</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>FCU_1F_002</t>
+          <t>VAV_1F_S15_096, VAV_1F_S15_097, VAV_1F_S15_098</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -37743,12 +37743,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-040_Head-Librarian-Office</t>
+          <t>entity:QNL_L1-047_Children-Library-Pre-School-Reading-And-Playing</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>L1.040 HEAD LIBRARIAN OFFICE</t>
+          <t>L1.047 CHILDREN LIBRARY PRE SCHOOL READING AND PLAYING</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -37758,27 +37758,27 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>L1.040</t>
+          <t>L1.047</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>VAV</t>
+          <t>VAV, CAV</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>VAV_1F_S15_005</t>
+          <t>CAV_1F_S11_006, CAV_1F_S11_008, CAV_1F_S11_009, VAV_1F_S15_006, VAV_1F_S15_007, VAV_1F_S15_008, VAV_1F_S15_009, VAV_1F_S15_010, VAV_1F_S15_011</t>
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -37789,12 +37789,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-041_Multipurpose-Room</t>
+          <t>entity:QNL_L1-048_Staff-Office</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>L1.041 MULTIPURPOSE ROOM</t>
+          <t>L1.048 STAFF OFFICE</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -37804,11 +37804,11 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>L1.041</t>
+          <t>L1.048</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -37817,11 +37817,11 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>VAV_1F_S15_096, VAV_1F_S15_097, VAV_1F_S15_098</t>
+          <t>VAV_1F_S15_012, VAV_1F_S15_039S</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -37835,12 +37835,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-047_Children-Library-Pre-School-Reading-And-Playing</t>
+          <t>entity:QNL_L1-063_Media-Studio-1</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>L1.047 CHILDREN LIBRARY PRE SCHOOL READING AND PLAYING</t>
+          <t>L1.063 MEDIA STUDIO 1</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -37850,24 +37850,24 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>L1.047</t>
+          <t>L1.063</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>VAV, CAV</t>
+          <t>VAV</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>CAV_1F_S11_006, CAV_1F_S11_008, CAV_1F_S11_009, VAV_1F_S15_006, VAV_1F_S15_007, VAV_1F_S15_008, VAV_1F_S15_009, VAV_1F_S15_010, VAV_1F_S15_011</t>
+          <t>VAV_1F_S15_001, VAV_1F_S15_002</t>
         </is>
       </c>
       <c r="I115" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -37881,12 +37881,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-048_Staff-Office</t>
+          <t>entity:QNL_L1-065_Media-Studio-1</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>L1.048 STAFF OFFICE</t>
+          <t>L1.065 MEDIA STUDIO 1</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -37896,7 +37896,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>L1.048</t>
+          <t>L1.065</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -37909,7 +37909,7 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>VAV_1F_S15_012, VAV_1F_S15_039S</t>
+          <t>VAV_1F_S15_003, VAV_1F_S15_004</t>
         </is>
       </c>
       <c r="I116" t="n">
@@ -37927,12 +37927,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-063_Media-Studio-1</t>
+          <t>entity:QNL_L1-067_Restaurant</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>L1.063 MEDIA STUDIO 1</t>
+          <t>L1.067 RESTAURANT</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -37942,27 +37942,27 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>L1.063</t>
+          <t>L1.067</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>VAV</t>
+          <t>KEF</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>VAV_1F_S15_001, VAV_1F_S15_002</t>
+          <t>KEF_101</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
@@ -37973,12 +37973,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-065_Media-Studio-1</t>
+          <t>entity:QNL_L1-080_Public-Services</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>L1.065 MEDIA STUDIO 1</t>
+          <t>L1.080 PUBLIC SERVICES</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -37988,11 +37988,11 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>L1.065</t>
+          <t>L1.080</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -38001,11 +38001,11 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>VAV_1F_S15_003, VAV_1F_S15_004</t>
+          <t>VAV_2F_S14_001, VAV_2F_S14_002, VAV_2F_S14_003, VAV_2F_S14_004</t>
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -38019,12 +38019,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-067_Restaurant</t>
+          <t>entity:QNL_L1-081_Bibliographer-1</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>L1.067 RESTAURANT</t>
+          <t>L1.081 BIBLIOGRAPHER 1</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -38034,7 +38034,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>L1.067</t>
+          <t>L1.081</t>
         </is>
       </c>
       <c r="F119" t="n">
@@ -38042,19 +38042,19 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>KEF</t>
+          <t>VAV</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>KEF_101</t>
+          <t>VAV_2F_S14_005</t>
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -38065,12 +38065,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-080_Public-Services</t>
+          <t>entity:QNL_L1-082_Bibliographer-2</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>L1.080 PUBLIC SERVICES</t>
+          <t>L1.082 BIBLIOGRAPHER 2</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -38080,11 +38080,11 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>L1.080</t>
+          <t>L1.082</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -38093,11 +38093,11 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>VAV_2F_S14_001, VAV_2F_S14_002, VAV_2F_S14_003, VAV_2F_S14_004</t>
+          <t>VAV_2F_S14_006</t>
         </is>
       </c>
       <c r="I120" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -38111,12 +38111,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-081_Bibliographer-1</t>
+          <t>entity:QNL_L1-083_Spec-Coll-And-Arch</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>L1.081 BIBLIOGRAPHER 1</t>
+          <t>L1.083 SPEC COLL AND ARCH</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -38126,7 +38126,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>L1.081</t>
+          <t>L1.083</t>
         </is>
       </c>
       <c r="F121" t="n">
@@ -38139,7 +38139,7 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>VAV_2F_S14_005</t>
+          <t>VAV_2F_S14_007</t>
         </is>
       </c>
       <c r="I121" t="n">
@@ -38157,12 +38157,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-082_Bibliographer-2</t>
+          <t>entity:QNL_L1-084_R-And-L-Services</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>L1.082 BIBLIOGRAPHER 2</t>
+          <t>L1.084 R AND L SERVICES</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -38172,7 +38172,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>L1.082</t>
+          <t>L1.084</t>
         </is>
       </c>
       <c r="F122" t="n">
@@ -38185,7 +38185,7 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>VAV_2F_S14_006</t>
+          <t>VAV_2F_S14_008</t>
         </is>
       </c>
       <c r="I122" t="n">
@@ -38203,12 +38203,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-083_Spec-Coll-And-Arch</t>
+          <t>entity:QNL_L1-085_Ad-Public-Service</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>L1.083 SPEC COLL AND ARCH</t>
+          <t>L1.085 AD PUBLIC SERVICE</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -38218,7 +38218,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>L1.083</t>
+          <t>L1.085</t>
         </is>
       </c>
       <c r="F123" t="n">
@@ -38231,7 +38231,7 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>VAV_2F_S14_007</t>
+          <t>VAV_2F_S14_009</t>
         </is>
       </c>
       <c r="I123" t="n">
@@ -38249,12 +38249,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-084_R-And-L-Services</t>
+          <t>entity:QNL_L1-086_Ref-Librarian-1</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>L1.084 R AND L SERVICES</t>
+          <t>L1.086 REF LIBRARIAN 1</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -38264,7 +38264,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>L1.084</t>
+          <t>L1.086</t>
         </is>
       </c>
       <c r="F124" t="n">
@@ -38277,7 +38277,7 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>VAV_2F_S14_008</t>
+          <t>VAV_2F_S14_010</t>
         </is>
       </c>
       <c r="I124" t="n">
@@ -38295,12 +38295,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-085_Ad-Public-Service</t>
+          <t>entity:QNL_L1-087_Ref-Librarian-2</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>L1.085 AD PUBLIC SERVICE</t>
+          <t>L1.087 REF LIBRARIAN 2</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -38310,7 +38310,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>L1.085</t>
+          <t>L1.087</t>
         </is>
       </c>
       <c r="F125" t="n">
@@ -38323,7 +38323,7 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>VAV_2F_S14_009</t>
+          <t>VAV_2F_S14_011</t>
         </is>
       </c>
       <c r="I125" t="n">
@@ -38341,12 +38341,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-086_Ref-Librarian-1</t>
+          <t>entity:QNL_L1-088_Ref-Librarian-3</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>L1.086 REF LIBRARIAN 1</t>
+          <t>L1.088 REF LIBRARIAN 3</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -38356,7 +38356,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>L1.086</t>
+          <t>L1.088</t>
         </is>
       </c>
       <c r="F126" t="n">
@@ -38369,7 +38369,7 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>VAV_2F_S14_010</t>
+          <t>VAV_2F_S14_012</t>
         </is>
       </c>
       <c r="I126" t="n">
@@ -38387,12 +38387,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-087_Ref-Librarian-2</t>
+          <t>entity:QNL_L1-089_Ref-Librarian-4</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>L1.087 REF LIBRARIAN 2</t>
+          <t>L1.089 REF LIBRARIAN 4</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -38402,7 +38402,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>L1.087</t>
+          <t>L1.089</t>
         </is>
       </c>
       <c r="F127" t="n">
@@ -38415,7 +38415,7 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>VAV_2F_S14_011</t>
+          <t>VAV_2F_S14_013</t>
         </is>
       </c>
       <c r="I127" t="n">
@@ -38433,12 +38433,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-088_Ref-Librarian-3</t>
+          <t>entity:QNL_L1-090_Ref-Librarian-5</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>L1.088 REF LIBRARIAN 3</t>
+          <t>L1.090 REF LIBRARIAN 5</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -38448,7 +38448,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>L1.088</t>
+          <t>L1.090</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -38461,7 +38461,7 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>VAV_2F_S14_012</t>
+          <t>VAV_2F_S14_014</t>
         </is>
       </c>
       <c r="I128" t="n">
@@ -38479,12 +38479,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-089_Ref-Librarian-4</t>
+          <t>entity:QNL_L1-091_Ref-Librarian-6</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>L1.089 REF LIBRARIAN 4</t>
+          <t>L1.091 REF LIBRARIAN 6</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -38494,7 +38494,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>L1.089</t>
+          <t>L1.091</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -38507,7 +38507,7 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>VAV_2F_S14_013</t>
+          <t>VAV_2F_S14_015</t>
         </is>
       </c>
       <c r="I129" t="n">
@@ -38525,12 +38525,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-090_Ref-Librarian-5</t>
+          <t>entity:QNL_L1-092_Ref-Librarian-7</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>L1.090 REF LIBRARIAN 5</t>
+          <t>L1.092 REF LIBRARIAN 7</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -38540,7 +38540,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>L1.090</t>
+          <t>L1.092</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -38553,7 +38553,7 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>VAV_2F_S14_014</t>
+          <t>VAV_2F_S14_016</t>
         </is>
       </c>
       <c r="I130" t="n">
@@ -38571,12 +38571,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-091_Ref-Librarian-6</t>
+          <t>entity:QNL_L1-093_Ref-Librarian-8</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>L1.091 REF LIBRARIAN 6</t>
+          <t>L1.093 REF LIBRARIAN 8</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -38586,7 +38586,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>L1.091</t>
+          <t>L1.093</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -38599,7 +38599,7 @@
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>VAV_2F_S14_015</t>
+          <t>VAV_2F_S14_017</t>
         </is>
       </c>
       <c r="I131" t="n">
@@ -38617,12 +38617,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-092_Ref-Librarian-7</t>
+          <t>entity:QNL_L1-094_Ref-Librarian-9</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>L1.092 REF LIBRARIAN 7</t>
+          <t>L1.094 REF LIBRARIAN 9</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -38632,7 +38632,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>L1.092</t>
+          <t>L1.094</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -38645,7 +38645,7 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>VAV_2F_S14_016</t>
+          <t>VAV_2F_S14_018</t>
         </is>
       </c>
       <c r="I132" t="n">
@@ -38663,12 +38663,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-093_Ref-Librarian-8</t>
+          <t>entity:QNL_L1-095_Ref-Librarian-10</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>L1.093 REF LIBRARIAN 8</t>
+          <t>L1.095 REF LIBRARIAN 10</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -38678,7 +38678,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>L1.093</t>
+          <t>L1.095</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -38691,7 +38691,7 @@
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>VAV_2F_S14_017</t>
+          <t>VAV_2F_S14_019</t>
         </is>
       </c>
       <c r="I133" t="n">
@@ -38709,12 +38709,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-094_Ref-Librarian-9</t>
+          <t>entity:QNL_L1-096_Ref-Librarian-11</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>L1.094 REF LIBRARIAN 9</t>
+          <t>L1.096 REF LIBRARIAN 11</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -38724,7 +38724,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>L1.094</t>
+          <t>L1.096</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -38737,7 +38737,7 @@
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>VAV_2F_S14_018</t>
+          <t>VAV_2F_S14_020</t>
         </is>
       </c>
       <c r="I134" t="n">
@@ -38755,12 +38755,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-095_Ref-Librarian-10</t>
+          <t>entity:QNL_L1-097_Ref-Librarian-12</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>L1.095 REF LIBRARIAN 10</t>
+          <t>L1.097 REF LIBRARIAN 12</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -38770,7 +38770,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>L1.095</t>
+          <t>L1.097</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -38783,7 +38783,7 @@
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>VAV_2F_S14_019</t>
+          <t>VAV_2F_S14_021</t>
         </is>
       </c>
       <c r="I135" t="n">
@@ -38801,12 +38801,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-096_Ref-Librarian-11</t>
+          <t>entity:QNL_L1-099_IDF-Room-02</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>L1.096 REF LIBRARIAN 11</t>
+          <t>L1.099 IDF ROOM 02</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -38816,7 +38816,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>L1.096</t>
+          <t>L1.099</t>
         </is>
       </c>
       <c r="F136" t="n">
@@ -38824,19 +38824,19 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>VAV</t>
+          <t>FCU</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>VAV_2F_S14_020</t>
+          <t>FCU_1F_003</t>
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137">
@@ -38847,12 +38847,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-097_Ref-Librarian-12</t>
+          <t>entity:QNL_L1-100_Aerial-Platform-Parking</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>L1.097 REF LIBRARIAN 12</t>
+          <t>L1.100 AERIAL PLATFORM PARKING</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -38862,24 +38862,24 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>L1.097</t>
+          <t>L1.100</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>VAV</t>
+          <t>CAV</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>VAV_2F_S14_021</t>
+          <t>CAV_1F_S15_004, CAV_1F_S15_018</t>
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -38893,12 +38893,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-099_IDF-Room-02</t>
+          <t>entity:QNL_L1-104_Prayer-Room-Female</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>L1.099 IDF ROOM 02</t>
+          <t>L1.104 PRAYER ROOM FEMALE</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -38908,27 +38908,27 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>L1.099</t>
+          <t>L1.104</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>FCU</t>
+          <t>VAV</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>FCU_1F_003</t>
+          <t>VAV_1F_S15_021, VAV_1F_S15_022, VAV_1F_S15_023, VAV_1F_S15_024</t>
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
@@ -38939,12 +38939,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-100_Aerial-Platform-Parking</t>
+          <t>entity:QNL_L1-105_Ablution-Men</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>L1.100 AERIAL PLATFORM PARKING</t>
+          <t>L1.105 ABLUTION MEN</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -38954,24 +38954,24 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>L1.100</t>
+          <t>L1.105</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>CAV</t>
+          <t>VAV</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>CAV_1F_S15_004, CAV_1F_S15_018</t>
+          <t>VAV_1F_S15_038</t>
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -38985,12 +38985,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-104_Prayer-Room-Female</t>
+          <t>entity:QNL_L1-106_Ablution-Women</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>L1.104 PRAYER ROOM FEMALE</t>
+          <t>L1.106 ABLUTION WOMEN</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -39000,11 +39000,11 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>L1.104</t>
+          <t>L1.106</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -39013,11 +39013,11 @@
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>VAV_1F_S15_021, VAV_1F_S15_022, VAV_1F_S15_023, VAV_1F_S15_024</t>
+          <t>VAV_1F_S15_025</t>
         </is>
       </c>
       <c r="I140" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -39031,12 +39031,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-105_Ablution-Men</t>
+          <t>entity:QNL_L1-144_ILL-Director</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>L1.105 ABLUTION MEN</t>
+          <t>L1.144 ILL DIRECTOR</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -39046,7 +39046,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>L1.105</t>
+          <t>L1.144</t>
         </is>
       </c>
       <c r="F141" t="n">
@@ -39054,12 +39054,12 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>VAV</t>
+          <t>FCU</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>VAV_1F_S15_038</t>
+          <t>FCU_1F_057</t>
         </is>
       </c>
       <c r="I141" t="n">
@@ -39077,12 +39077,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-106_Ablution-Women</t>
+          <t>entity:QNL_L1-145_ILL-Director</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>L1.106 ABLUTION WOMEN</t>
+          <t>L1.145 ILL DIRECTOR</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -39092,7 +39092,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>L1.106</t>
+          <t>L1.145</t>
         </is>
       </c>
       <c r="F142" t="n">
@@ -39100,12 +39100,12 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>VAV</t>
+          <t>FCU</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>VAV_1F_S15_025</t>
+          <t>FCU_1F_058</t>
         </is>
       </c>
       <c r="I142" t="n">
@@ -39123,12 +39123,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-144_ILL-Director</t>
+          <t>entity:QNL_L1-150_Restaurant</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>L1.144 ILL DIRECTOR</t>
+          <t>L1.150 RESTAURANT</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -39138,24 +39138,24 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>L1.144</t>
+          <t>L1.150</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>FCU</t>
+          <t>FCU, CAV</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>FCU_1F_057</t>
+          <t>CAV_1F_S15_002, CAV_1F_S15_005, CAV_1F_S15_006, CAV_1F_S15_010, CAV_1F_S15_011, CAV_1F_S15_012, CAV_1F_S15_013, CAV_1F_S15_014, CAV_1F_S15_015, CAV_1F_S15_016, CAV_1F_S15_017, FCU_1F_059, FCU_1F_060, FCU_1F_061, FCU_1F_062, FCU_1F_063, FCU_1F_064</t>
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -39169,12 +39169,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-145_ILL-Director</t>
+          <t>entity:QNL_L1-153_Furniture-Store</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>L1.145 ILL DIRECTOR</t>
+          <t>L1.153 FURNITURE STORE</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -39184,7 +39184,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>L1.145</t>
+          <t>L1.153</t>
         </is>
       </c>
       <c r="F144" t="n">
@@ -39192,12 +39192,12 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>FCU</t>
+          <t>CAV</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>FCU_1F_058</t>
+          <t>CAV_1F_S15_019</t>
         </is>
       </c>
       <c r="I144" t="n">
@@ -39215,12 +39215,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-150_Restaurant</t>
+          <t>entity:QNL_L1-990_Vestibule</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>L1.150 RESTAURANT</t>
+          <t>L1.990 VESTIBULE</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -39230,24 +39230,24 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>L1.150</t>
+          <t>L1.990</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>FCU, CAV</t>
+          <t>FCU</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>CAV_1F_S15_002, CAV_1F_S15_005, CAV_1F_S15_006, CAV_1F_S15_010, CAV_1F_S15_011, CAV_1F_S15_012, CAV_1F_S15_013, CAV_1F_S15_014, CAV_1F_S15_015, CAV_1F_S15_016, CAV_1F_S15_017, FCU_1F_059, FCU_1F_060, FCU_1F_061, FCU_1F_062, FCU_1F_063, FCU_1F_064</t>
+          <t>FCU_1F_055</t>
         </is>
       </c>
       <c r="I145" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -39261,12 +39261,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-153_Furniture-Store</t>
+          <t>entity:QNL_L1-991_External-Book-Drop</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>L1.153 FURNITURE STORE</t>
+          <t>L1.991 EXTERNAL BOOK DROP</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -39276,7 +39276,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>L1.153</t>
+          <t>L1.991</t>
         </is>
       </c>
       <c r="F146" t="n">
@@ -39284,12 +39284,12 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>CAV</t>
+          <t>FCU</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>CAV_1F_S15_019</t>
+          <t>FCU_1F_056</t>
         </is>
       </c>
       <c r="I146" t="n">
@@ -39307,12 +39307,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-990_Vestibule</t>
+          <t>entity:QNL_L1-BC1_Bridge-Ceiling</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>L1.990 VESTIBULE</t>
+          <t>BC1 BRIDGE CEILING</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -39322,7 +39322,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>L1.990</t>
+          <t>L1.BC1</t>
         </is>
       </c>
       <c r="F147" t="n">
@@ -39335,7 +39335,7 @@
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>FCU_1F_055</t>
+          <t>FCU_1F_016</t>
         </is>
       </c>
       <c r="I147" t="n">
@@ -39353,12 +39353,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-991_External-Book-Drop</t>
+          <t>entity:QNL_L1-BC2_Bridge-Ceiling</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>L1.991 EXTERNAL BOOK DROP</t>
+          <t>BC2 BRIDGE CEILING</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -39368,7 +39368,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>L1.991</t>
+          <t>L1.BC2</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -39381,7 +39381,7 @@
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>FCU_1F_056</t>
+          <t>FCU_1F_041</t>
         </is>
       </c>
       <c r="I148" t="n">
@@ -39399,12 +39399,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-BC1_Bridge-Ceiling</t>
+          <t>entity:QNL_L1-BI_Bridge-IDF</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>BC1 BRIDGE CEILING</t>
+          <t>BI BRIDGE IDF</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -39414,7 +39414,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>L1.BC1</t>
+          <t>L1.BI</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -39427,14 +39427,14 @@
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>FCU_1F_016</t>
+          <t>FCU_1F_065</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -39445,12 +39445,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-BC2_Bridge-Ceiling</t>
+          <t>entity:QNL_L1-BR1_Bridge-Ceiling-Void</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>BC2 BRIDGE CEILING</t>
+          <t>BR1 BRIDGE CEILING VOID</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -39460,11 +39460,11 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>L1.BC2</t>
+          <t>L1.BR1</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -39473,11 +39473,11 @@
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>FCU_1F_041</t>
+          <t>FCU_1F_031, FCU_1F_032, FCU_1F_033, FCU_1F_034, FCU_1F_047, FCU_1F_048</t>
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -39491,12 +39491,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-BI_Bridge-IDF</t>
+          <t>entity:QNL_L1-BR2_Bridge-Ceiling-Void</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>BI BRIDGE IDF</t>
+          <t>BR2 BRIDGE CEILING VOID</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -39506,11 +39506,11 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>L1.BI</t>
+          <t>L1.BR2</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -39519,14 +39519,14 @@
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>FCU_1F_065</t>
+          <t>FCU_1F_025, FCU_1F_027, FCU_1F_029, FCU_1F_030, FCU_1F_035, FCU_1F_036, FCU_1F_049, FCU_1F_050</t>
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -39537,12 +39537,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-BR1_Bridge-Ceiling-Void</t>
+          <t>entity:QNL_L1-BR3_Bridge-Ceiling-Void</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>BR1 BRIDGE CEILING VOID</t>
+          <t>BR3 BRIDGE CEILING VOID</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -39552,7 +39552,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>L1.BR1</t>
+          <t>L1.BR3</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -39565,7 +39565,7 @@
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>FCU_1F_031, FCU_1F_032, FCU_1F_033, FCU_1F_034, FCU_1F_047, FCU_1F_048</t>
+          <t>FCU_1F_020, FCU_1F_022, FCU_1F_023, FCU_1F_024, FCU_1F_037, FCU_1F_038</t>
         </is>
       </c>
       <c r="I152" t="n">
@@ -39583,12 +39583,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-BR2_Bridge-Ceiling-Void</t>
+          <t>entity:QNL_L1-BR4_Bridge-Ceiling-Void</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>BR2 BRIDGE CEILING VOID</t>
+          <t>BR4 BRIDGE CEILING VOID</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -39598,11 +39598,11 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>L1.BR2</t>
+          <t>L1.BR4</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -39611,11 +39611,11 @@
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>FCU_1F_025, FCU_1F_027, FCU_1F_029, FCU_1F_030, FCU_1F_035, FCU_1F_036, FCU_1F_049, FCU_1F_050</t>
+          <t>FCU_1F_014, FCU_1F_017, FCU_1F_018, FCU_1F_026, FCU_1F_028, FCU_1F_039, FCU_1F_040, FCU_1F_051, FCU_1F_052</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -39629,12 +39629,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-BR3_Bridge-Ceiling-Void</t>
+          <t>entity:QNL_L1-BR5_Bridge-Ceiling-Void</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>BR3 BRIDGE CEILING VOID</t>
+          <t>BR5 BRIDGE CEILING VOID</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -39644,11 +39644,11 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>L1.BR3</t>
+          <t>L1.BR5</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -39657,11 +39657,11 @@
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>FCU_1F_020, FCU_1F_022, FCU_1F_023, FCU_1F_024, FCU_1F_037, FCU_1F_038</t>
+          <t>FCU_1F_009, FCU_1F_010, FCU_1F_011, FCU_1F_012, FCU_1F_019, FCU_1F_021, FCU_1F_042, FCU_1F_053, FCU_1F_054</t>
         </is>
       </c>
       <c r="I154" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -39675,12 +39675,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-BR4_Bridge-Ceiling-Void</t>
+          <t>entity:QNL_L1-BR6_Bridge-Ceiling-Void</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>BR4 BRIDGE CEILING VOID</t>
+          <t>BR6 BRIDGE CEILING VOID</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -39690,11 +39690,11 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>L1.BR4</t>
+          <t>L1.BR6</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -39703,11 +39703,11 @@
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>FCU_1F_014, FCU_1F_017, FCU_1F_018, FCU_1F_026, FCU_1F_028, FCU_1F_039, FCU_1F_040, FCU_1F_051, FCU_1F_052</t>
+          <t>FCU_1F_004, FCU_1F_005, FCU_1F_006, FCU_1F_007, FCU_1F_008, FCU_1F_013, FCU_1F_015, FCU_1F_043, FCU_1F_044, FCU_1F_045, FCU_1F_046</t>
         </is>
       </c>
       <c r="I155" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -39721,12 +39721,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-BR5_Bridge-Ceiling-Void</t>
+          <t>entity:QNL_L1-E1_Shaft</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>BR5 BRIDGE CEILING VOID</t>
+          <t>E1 SHAFT</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -39736,27 +39736,27 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>L1.BR5</t>
+          <t>L1.E1</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>FCU</t>
+          <t>TEF</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>FCU_1F_009, FCU_1F_010, FCU_1F_011, FCU_1F_012, FCU_1F_019, FCU_1F_021, FCU_1F_042, FCU_1F_053, FCU_1F_054</t>
+          <t>TEF_102C</t>
         </is>
       </c>
       <c r="I156" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157">
@@ -39767,12 +39767,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-BR6_Bridge-Ceiling-Void</t>
+          <t>entity:QNL_L1-E2_Shaft</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>BR6 BRIDGE CEILING VOID</t>
+          <t>E2 SHAFT</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -39782,27 +39782,27 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>L1.BR6</t>
+          <t>L1.E2</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>FCU</t>
+          <t>TEF</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>FCU_1F_004, FCU_1F_005, FCU_1F_006, FCU_1F_007, FCU_1F_008, FCU_1F_013, FCU_1F_015, FCU_1F_043, FCU_1F_044, FCU_1F_045, FCU_1F_046</t>
+          <t>TEF_101C</t>
         </is>
       </c>
       <c r="I157" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158">
@@ -39813,12 +39813,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-E1_Shaft</t>
+          <t>entity:QNL_L1-L-3_L-3</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>E1 SHAFT</t>
+          <t>L-3 L 3</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -39828,7 +39828,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>L1.E1</t>
+          <t>L1.L-3</t>
         </is>
       </c>
       <c r="F158" t="n">
@@ -39836,12 +39836,12 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>TEF</t>
+          <t>EF</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>TEF_102C</t>
+          <t>EF_201</t>
         </is>
       </c>
       <c r="I158" t="n">
@@ -39859,22 +39859,22 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-E2_Shaft</t>
+          <t>entity:QNL_L2-009_KDF-Room</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>E2 SHAFT</t>
+          <t>L2.009 KDF ROOM</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>L1.E2</t>
+          <t>L2.009</t>
         </is>
       </c>
       <c r="F159" t="n">
@@ -39882,12 +39882,12 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>TEF</t>
+          <t>FCU</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>TEF_101C</t>
+          <t>FCU_2F_005</t>
         </is>
       </c>
       <c r="I159" t="n">
@@ -39905,22 +39905,22 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-L-3_L-3</t>
+          <t>entity:QNL_L2-010_Breakout-Space</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>L-3 L 3</t>
+          <t>L2.010 BREAKOUT SPACE</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>L1.L-3</t>
+          <t>L2.010</t>
         </is>
       </c>
       <c r="F160" t="n">
@@ -39928,19 +39928,19 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>EF</t>
+          <t>VAV</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>EF_201</t>
+          <t>VAV_2F_S12_021</t>
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
@@ -39951,12 +39951,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>entity:QNL_L2-009_KDF-Room</t>
+          <t>entity:QNL_L2-011_Circulation-Office</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>L2.009 KDF ROOM</t>
+          <t>L2.011 CIRCULATION OFFICE</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -39966,27 +39966,27 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>L2.009</t>
+          <t>L2.011</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>FCU</t>
+          <t>VAV</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>FCU_2F_005</t>
+          <t>VAV_2F_S12_022, VAV_2F_S12_026</t>
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
@@ -39997,12 +39997,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>entity:QNL_L2-010_Breakout-Space</t>
+          <t>entity:QNL_L2-012_Office-Spec-Col</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>L2.010 BREAKOUT SPACE</t>
+          <t>L2.012 OFFICE SPEC COL</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -40012,7 +40012,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>L2.010</t>
+          <t>L2.012</t>
         </is>
       </c>
       <c r="F162" t="n">
@@ -40025,7 +40025,7 @@
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>VAV_2F_S12_021</t>
+          <t>VAV_2F_S12_023</t>
         </is>
       </c>
       <c r="I162" t="n">
@@ -40043,12 +40043,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>entity:QNL_L2-011_Circulation-Office</t>
+          <t>entity:QNL_L2-013_Office-Spec-Col</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>L2.011 CIRCULATION OFFICE</t>
+          <t>L2.013 OFFICE SPEC COL</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -40058,11 +40058,11 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>L2.011</t>
+          <t>L2.013</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -40071,11 +40071,11 @@
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>VAV_2F_S12_022, VAV_2F_S12_026</t>
+          <t>VAV_2F_S12_024</t>
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -40089,12 +40089,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>entity:QNL_L2-012_Office-Spec-Col</t>
+          <t>entity:QNL_L2-014_Trans-Spc-And-Space-Ed</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>L2.012 OFFICE SPEC COL</t>
+          <t>L2.014 TRANS SPC AND SPACE ED</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -40104,7 +40104,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>L2.012</t>
+          <t>L2.014</t>
         </is>
       </c>
       <c r="F164" t="n">
@@ -40117,7 +40117,7 @@
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>VAV_2F_S12_023</t>
+          <t>VAV_2F_S13_004</t>
         </is>
       </c>
       <c r="I164" t="n">
@@ -40135,12 +40135,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>entity:QNL_L2-013_Office-Spec-Col</t>
+          <t>entity:QNL_L2-017_40-Group-Study-Room-7</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>L2.013 OFFICE SPEC COL</t>
+          <t>L2.017 40 GROUP STUDY ROOM 7</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -40150,11 +40150,11 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>L2.013</t>
+          <t>L2.017</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
@@ -40163,11 +40163,11 @@
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>VAV_2F_S12_024</t>
+          <t>VAV_2F_S12_027, VAV_2F_S12_029</t>
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -40181,12 +40181,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>entity:QNL_L2-014_Trans-Spc-And-Space-Ed</t>
+          <t>entity:QNL_L2-018_Group-Study-Room-8</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>L2.014 TRANS SPC AND SPACE ED</t>
+          <t>L2.018 GROUP STUDY ROOM 8</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -40196,11 +40196,11 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>L2.014</t>
+          <t>L2.018</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -40209,11 +40209,11 @@
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>VAV_2F_S13_004</t>
+          <t>VAV_2F_S12_028, VAV_2F_S12_097</t>
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -40227,12 +40227,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>entity:QNL_L2-017_40-Group-Study-Room-7</t>
+          <t>entity:QNL_L2-021_Libr-Com-Rel-Spc-And-Events-Spc</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>L2.017 40 GROUP STUDY ROOM 7</t>
+          <t>L2.021 LIBR COM REL SPC AND EVENTS SPC</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -40242,11 +40242,11 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>L2.017</t>
+          <t>L2.021</t>
         </is>
       </c>
       <c r="F167" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
@@ -40255,11 +40255,11 @@
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>VAV_2F_S12_027, VAV_2F_S12_029</t>
+          <t>VAV_2F_S13_005</t>
         </is>
       </c>
       <c r="I167" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -40273,12 +40273,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>entity:QNL_L2-018_Group-Study-Room-8</t>
+          <t>entity:QNL_L2-022_Academic-Pers-Libraria</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>L2.018 GROUP STUDY ROOM 8</t>
+          <t>L2.022 ACADEMIC PERS LIBRARIA</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -40288,11 +40288,11 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>L2.018</t>
+          <t>L2.022</t>
         </is>
       </c>
       <c r="F168" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
@@ -40301,11 +40301,11 @@
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>VAV_2F_S12_028, VAV_2F_S12_097</t>
+          <t>VAV_2F_S13_006</t>
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -40319,12 +40319,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>entity:QNL_L2-021_Libr-Com-Rel-Spc-And-Events-Spc</t>
+          <t>entity:QNL_L2-023_Ad-Admin-And-Planning</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>L2.021 LIBR COM REL SPC AND EVENTS SPC</t>
+          <t>L2.023 AD ADMIN AND PLANNING</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -40334,7 +40334,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>L2.021</t>
+          <t>L2.023</t>
         </is>
       </c>
       <c r="F169" t="n">
@@ -40347,7 +40347,7 @@
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>VAV_2F_S13_005</t>
+          <t>VAV_2F_S13_007</t>
         </is>
       </c>
       <c r="I169" t="n">
@@ -40365,12 +40365,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>entity:QNL_L2-022_Academic-Pers-Libraria</t>
+          <t>entity:QNL_L2-024_Office-Coord</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>L2.022 ACADEMIC PERS LIBRARIA</t>
+          <t>L2.024 OFFICE COORD</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -40380,7 +40380,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>L2.022</t>
+          <t>L2.024</t>
         </is>
       </c>
       <c r="F170" t="n">
@@ -40393,7 +40393,7 @@
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>VAV_2F_S13_006</t>
+          <t>VAV_2F_S13_008</t>
         </is>
       </c>
       <c r="I170" t="n">
@@ -40411,12 +40411,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>entity:QNL_L2-023_Ad-Admin-And-Planning</t>
+          <t>entity:QNL_L2-025_Open-Office</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>L2.023 AD ADMIN AND PLANNING</t>
+          <t>L2.025 OPEN OFFICE</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -40426,7 +40426,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>L2.023</t>
+          <t>L2.025</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -40439,7 +40439,7 @@
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>VAV_2F_S13_007</t>
+          <t>VAV_2F_S13_009</t>
         </is>
       </c>
       <c r="I171" t="n">
@@ -40457,12 +40457,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>entity:QNL_L2-024_Office-Coord</t>
+          <t>entity:QNL_L2-043_Service-And-Lounge</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>L2.024 OFFICE COORD</t>
+          <t>L2.043 SERVICE AND LOUNGE</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -40472,7 +40472,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>L2.024</t>
+          <t>L2.043</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -40485,7 +40485,7 @@
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>VAV_2F_S13_008</t>
+          <t>VAV_2F_S13_003</t>
         </is>
       </c>
       <c r="I172" t="n">
@@ -40503,12 +40503,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>entity:QNL_L2-025_Open-Office</t>
+          <t>entity:QNL_L2-044_Lib-Directors-Room</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>L2.025 OPEN OFFICE</t>
+          <t>L2.044 LIB DIRECTOR S ROOM</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -40518,11 +40518,11 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>L2.025</t>
+          <t>L2.044</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
@@ -40531,14 +40531,14 @@
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>VAV_2F_S13_009</t>
+          <t>VAV_2F_S13_001, VAV_2F_S13_002</t>
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J173" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
@@ -40549,12 +40549,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>entity:QNL_L2-043_Service-And-Lounge</t>
+          <t>entity:QNL_L2-046_VIP-Meeting</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>L2.043 SERVICE AND LOUNGE</t>
+          <t>L2.046 VIP MEETING</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -40564,7 +40564,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>L2.043</t>
+          <t>L2.046</t>
         </is>
       </c>
       <c r="F174" t="n">
@@ -40577,14 +40577,14 @@
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>VAV_2F_S13_003</t>
+          <t>VAV_2F_S15_005</t>
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175">
@@ -40595,12 +40595,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>entity:QNL_L2-044_Lib-Directors-Room</t>
+          <t>entity:QNL_L2-048_VIP-Wating</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>L2.044 LIB DIRECTOR S ROOM</t>
+          <t>L2.048 VIP WATING</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -40610,11 +40610,11 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>L2.044</t>
+          <t>L2.048</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
@@ -40623,14 +40623,14 @@
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>VAV_2F_S13_001, VAV_2F_S13_002</t>
+          <t>VAV_2F_S13_016</t>
         </is>
       </c>
       <c r="I175" t="n">
         <v>0</v>
       </c>
       <c r="J175" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="176">
@@ -40641,12 +40641,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>entity:QNL_L2-046_VIP-Meeting</t>
+          <t>entity:QNL_L2-051_VIP-Room</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>L2.046 VIP MEETING</t>
+          <t>L2.051 VIP ROOM</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -40656,11 +40656,11 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>L2.046</t>
+          <t>L2.051</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
@@ -40669,14 +40669,14 @@
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>VAV_2F_S15_005</t>
+          <t>VAV_2F_S15_001, VAV_2F_S15_002, VAV_2F_S15_003, VAV_2F_S15_004</t>
         </is>
       </c>
       <c r="I176" t="n">
         <v>0</v>
       </c>
       <c r="J176" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="177">
@@ -40687,12 +40687,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>entity:QNL_L2-048_VIP-Wating</t>
+          <t>entity:QNL_L2-070_Indivistudy-Room</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>L2.048 VIP WATING</t>
+          <t>L2.070 INDIVISTUDY ROOM</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -40702,27 +40702,27 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>L2.048</t>
+          <t>L2.070</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>VAV</t>
+          <t>FCU</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>VAV_2F_S13_016</t>
+          <t>FCU_2F_048, FCU_2F_049, FCU_2F_050</t>
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
@@ -40733,12 +40733,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>entity:QNL_L2-051_VIP-Room</t>
+          <t>entity:QNL_L2-073_Indivistudy-Room</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>L2.051 VIP ROOM</t>
+          <t>L2.073 INDIVISTUDY ROOM</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -40748,27 +40748,27 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>L2.051</t>
+          <t>L2.073</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>VAV</t>
+          <t>FCU</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>VAV_2F_S15_001, VAV_2F_S15_002, VAV_2F_S15_003, VAV_2F_S15_004</t>
+          <t>FCU_2F_051, FCU_2F_052, FCU_2F_053</t>
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J178" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179">
@@ -40779,12 +40779,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>entity:QNL_L2-070_Indivistudy-Room</t>
+          <t>entity:QNL_L2-076_Group-Study-Room</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>L2.070 INDIVISTUDY ROOM</t>
+          <t>L2.076 GROUP STUDY ROOM</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -40794,11 +40794,11 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>L2.070</t>
+          <t>L2.076</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
@@ -40807,11 +40807,11 @@
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>FCU_2F_048, FCU_2F_049, FCU_2F_050</t>
+          <t>FCU_2F_046, FCU_2F_047</t>
         </is>
       </c>
       <c r="I179" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -40825,12 +40825,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>entity:QNL_L2-073_Indivistudy-Room</t>
+          <t>entity:QNL_L2-081_Group-Study-Room</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>L2.073 INDIVISTUDY ROOM</t>
+          <t>L2.081 GROUP STUDY ROOM</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -40840,11 +40840,11 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>L2.073</t>
+          <t>L2.081</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
@@ -40853,11 +40853,11 @@
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>FCU_2F_051, FCU_2F_052, FCU_2F_053</t>
+          <t>FCU_2F_045</t>
         </is>
       </c>
       <c r="I180" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -40871,12 +40871,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>entity:QNL_L2-076_Group-Study-Room</t>
+          <t>entity:QNL_L2-087_Auditorium-High-Levlel-In-Ceiling-Void</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>L2.076 GROUP STUDY ROOM</t>
+          <t>L2.087 AUDITORIUM HIGH LEVLEL IN CEILING VOID</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -40886,11 +40886,11 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>L2.076</t>
+          <t>L2.087</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
@@ -40899,11 +40899,11 @@
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>FCU_2F_046, FCU_2F_047</t>
+          <t>FCU_2F_034, FCU_2F_035, FCU_2F_036, FCU_2F_037, FCU_2F_038, FCU_2F_039, FCU_2F_040</t>
         </is>
       </c>
       <c r="I181" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -40917,12 +40917,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>entity:QNL_L2-081_Group-Study-Room</t>
+          <t>entity:QNL_L2-088_Bridge-Raised-Floor</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>L2.081 GROUP STUDY ROOM</t>
+          <t>L2.088 BRIDGE RAISED FLOOR</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -40932,11 +40932,11 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>L2.081</t>
+          <t>L2.088</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
@@ -40945,11 +40945,11 @@
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>FCU_2F_045</t>
+          <t>FCU_2F_041, FCU_2F_042, FCU_2F_043, FCU_2F_044</t>
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -40963,12 +40963,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>entity:QNL_L2-087_Auditorium-High-Levlel-In-Ceiling-Void</t>
+          <t>entity:QNL_L2-088_Lounge-Area</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>L2.087 AUDITORIUM HIGH LEVLEL IN CEILING VOID</t>
+          <t>L2.088 LOUNGE AREA</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -40978,11 +40978,11 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>L2.087</t>
+          <t>L2.088</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
@@ -40991,11 +40991,11 @@
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>FCU_2F_034, FCU_2F_035, FCU_2F_036, FCU_2F_037, FCU_2F_038, FCU_2F_039, FCU_2F_040</t>
+          <t>FCU_2F_054, FCU_2F_055</t>
         </is>
       </c>
       <c r="I183" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -41009,12 +41009,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>entity:QNL_L2-088_Bridge-Raised-Floor</t>
+          <t>entity:QNL_L2-992_Gulf-Material</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>L2.088 BRIDGE RAISED FLOOR</t>
+          <t>L2.992 GULF MATERIAL</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -41024,24 +41024,24 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>L2.088</t>
+          <t>L2.992</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>FCU</t>
+          <t>VAV</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>FCU_2F_041, FCU_2F_042, FCU_2F_043, FCU_2F_044</t>
+          <t>VAV_2F_S10_001, VAV_2F_S10_002, VAV_2F_S10_003, VAV_2F_S10_004, VAV_2F_S10_005, VAV_2F_S10_006</t>
         </is>
       </c>
       <c r="I184" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -41055,12 +41055,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>entity:QNL_L2-088_Lounge-Area</t>
+          <t>entity:QNL_L2-993_Corridor</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>L2.088 LOUNGE AREA</t>
+          <t>L2.993 CORRIDOR</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -41070,24 +41070,24 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>L2.088</t>
+          <t>L2.993</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>FCU</t>
+          <t>VAV</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>FCU_2F_054, FCU_2F_055</t>
+          <t>VAV_2F_S12_025, VAV_2F_S13_010, VAV_2F_S13_011, VAV_2F_S13_012, VAV_2F_S13_013, VAV_2F_S13_014, VAV_2F_S13_015</t>
         </is>
       </c>
       <c r="I185" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -41101,42 +41101,42 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>entity:QNL_L2-992_Gulf-Material</t>
+          <t>entity:QNL_P-002_Plant-Zone</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>L2.992 GULF MATERIAL</t>
+          <t>P.002 PLANT ZONE</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>L2.992</t>
+          <t>P.002</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>VAV</t>
+          <t>EF, SEF</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>VAV_2F_S10_001, VAV_2F_S10_002, VAV_2F_S10_003, VAV_2F_S10_004, VAV_2F_S10_005, VAV_2F_S10_006</t>
+          <t>EF_RP01, SEF_RP04, SEF_RP05, SEF_RP06, SEF_ZoneA</t>
         </is>
       </c>
       <c r="I186" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J186" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="187">
@@ -41147,22 +41147,22 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>entity:QNL_L2-993_Corridor</t>
+          <t>entity:QNL_P-004_Plant-Zone</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>L2.993 CORRIDOR</t>
+          <t>P.004 PLANT ZONE</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>L2.993</t>
+          <t>P.004</t>
         </is>
       </c>
       <c r="F187" t="n">
@@ -41170,19 +41170,19 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>VAV</t>
+          <t>DX Unit, EF, SEF</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>VAV_2F_S12_025, VAV_2F_S13_010, VAV_2F_S13_011, VAV_2F_S13_012, VAV_2F_S13_013, VAV_2F_S13_014, VAV_2F_S13_015</t>
+          <t>DX_B21, DX_B24, EF_RP02, SEF_RP07, SEF_RP08, SEF_RP09, SEF_ZoneB</t>
         </is>
       </c>
       <c r="I187" t="n">
+        <v>0</v>
+      </c>
+      <c r="J187" t="n">
         <v>7</v>
-      </c>
-      <c r="J187" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="188">
@@ -41193,12 +41193,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>entity:QNL_P-002_Plant-Zone</t>
+          <t>entity:QNL_P-006_Plant-Zone</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>P.002 PLANT ZONE</t>
+          <t>P.006 PLANT ZONE</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -41208,27 +41208,27 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>P.002</t>
+          <t>P.006</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>EF, SEF</t>
+          <t>SEF</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>EF_RP01, SEF_RP04, SEF_RP05, SEF_RP06, SEF_ZoneA</t>
+          <t>SEF_RP11, SEF_RP12</t>
         </is>
       </c>
       <c r="I188" t="n">
         <v>0</v>
       </c>
       <c r="J188" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="189">
@@ -41239,12 +41239,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>entity:QNL_P-004_Plant-Zone</t>
+          <t>entity:QNL_P-007_Plant-Zone</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>P.004 PLANT ZONE</t>
+          <t>P.007 PLANT ZONE</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -41254,27 +41254,27 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>P.004</t>
+          <t>P.007</t>
         </is>
       </c>
       <c r="F189" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>DX Unit, EF, SEF</t>
+          <t>EF, SEF</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>DX_B21, DX_B24, EF_RP02, SEF_RP07, SEF_RP08, SEF_RP09, SEF_ZoneB</t>
+          <t>EF_RP03, SEF_RP10, SEF_ZoneC</t>
         </is>
       </c>
       <c r="I189" t="n">
         <v>0</v>
       </c>
       <c r="J189" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="190">
@@ -41285,42 +41285,42 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>entity:QNL_P-006_Plant-Zone</t>
+          <t>entity:QNL_T1-020_Open-Lounge-Terrace</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>P.006 PLANT ZONE</t>
+          <t>T1.020 OPEN LOUNGE TERRACE</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>P.006</t>
+          <t>T1.020</t>
         </is>
       </c>
       <c r="F190" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>SEF</t>
+          <t>FCU</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>SEF_RP11, SEF_RP12</t>
+          <t>FCU_2F_060, FCU_2F_061, FCU_2F_062</t>
         </is>
       </c>
       <c r="I190" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J190" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191">
@@ -41331,42 +41331,42 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>entity:QNL_P-007_Plant-Zone</t>
+          <t>entity:QNL_T1-021_Open-Study-Terrace</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>P.007 PLANT ZONE</t>
+          <t>T1.021 OPEN STUDY TERRACE</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>P.007</t>
+          <t>T1.021</t>
         </is>
       </c>
       <c r="F191" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>EF, SEF</t>
+          <t>FCU</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>EF_RP03, SEF_RP10, SEF_ZoneC</t>
+          <t>FCU_2F_056, FCU_2F_057, FCU_2F_058, FCU_2F_059</t>
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J191" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192">
@@ -41377,12 +41377,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>entity:QNL_T1-020_Open-Lounge-Terrace</t>
+          <t>entity:QNL_T1-171_IDF-Room</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>T1.020 OPEN LOUNGE TERRACE</t>
+          <t>T1.171 IDF ROOM</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -41392,11 +41392,11 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>T1.020</t>
+          <t>T1.171</t>
         </is>
       </c>
       <c r="F192" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
@@ -41405,14 +41405,14 @@
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>FCU_2F_060, FCU_2F_061, FCU_2F_062</t>
+          <t>FCU_2F_003</t>
         </is>
       </c>
       <c r="I192" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193">
@@ -41423,12 +41423,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>entity:QNL_T1-021_Open-Study-Terrace</t>
+          <t>entity:QNL_T1-275_IDF-Room</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>T1.021 OPEN STUDY TERRACE</t>
+          <t>T1.275 IDF ROOM</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -41438,11 +41438,11 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>T1.021</t>
+          <t>T1.275</t>
         </is>
       </c>
       <c r="F193" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
@@ -41451,14 +41451,14 @@
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>FCU_2F_056, FCU_2F_057, FCU_2F_058, FCU_2F_059</t>
+          <t>FCU_2F_001</t>
         </is>
       </c>
       <c r="I193" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="194">
@@ -41469,12 +41469,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>entity:QNL_T1-171_IDF-Room</t>
+          <t>entity:QNL_T1-276_IDF-Room</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>T1.171 IDF ROOM</t>
+          <t>T1.276 IDF ROOM</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -41484,7 +41484,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>T1.171</t>
+          <t>T1.276</t>
         </is>
       </c>
       <c r="F194" t="n">
@@ -41497,7 +41497,7 @@
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>FCU_2F_003</t>
+          <t>FCU_2F_002</t>
         </is>
       </c>
       <c r="I194" t="n">
@@ -41515,12 +41515,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>entity:QNL_T1-275_IDF-Room</t>
+          <t>entity:QNL_T1-323_IDF-Room</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>T1.275 IDF ROOM</t>
+          <t>T1.323 IDF ROOM</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -41530,7 +41530,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>T1.275</t>
+          <t>T1.323</t>
         </is>
       </c>
       <c r="F195" t="n">
@@ -41543,7 +41543,7 @@
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>FCU_2F_001</t>
+          <t>FCU_1F_001</t>
         </is>
       </c>
       <c r="I195" t="n">
@@ -41561,12 +41561,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>entity:QNL_T1-276_IDF-Room</t>
+          <t>entity:QNL_T1-1714_IDF-Room</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>T1.276 IDF ROOM</t>
+          <t>T1.1714 IDF ROOM</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -41576,7 +41576,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>T1.276</t>
+          <t>T1.1714</t>
         </is>
       </c>
       <c r="F196" t="n">
@@ -41589,7 +41589,7 @@
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>FCU_2F_002</t>
+          <t>FCU_2F_004</t>
         </is>
       </c>
       <c r="I196" t="n">
@@ -41599,100 +41599,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>QNL</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>entity:QNL_T1-323_IDF-Room</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>T1.323 IDF ROOM</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>T1.323</t>
-        </is>
-      </c>
-      <c r="F197" t="n">
-        <v>1</v>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>FCU</t>
-        </is>
-      </c>
-      <c r="H197" s="2" t="inlineStr">
-        <is>
-          <t>FCU_1F_001</t>
-        </is>
-      </c>
-      <c r="I197" t="n">
-        <v>0</v>
-      </c>
-      <c r="J197" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>QNL</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>entity:QNL_T1-1714_IDF-Room</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>T1.1714 IDF ROOM</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>T1.1714</t>
-        </is>
-      </c>
-      <c r="F198" t="n">
-        <v>1</v>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>FCU</t>
-        </is>
-      </c>
-      <c r="H198" s="2" t="inlineStr">
-        <is>
-          <t>FCU_2F_004</t>
-        </is>
-      </c>
-      <c r="I198" t="n">
-        <v>0</v>
-      </c>
-      <c r="J198" t="n">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J198"/>
+  <autoFilter ref="A1:J196"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/projects/dar-cairo-room-naming/Rooms_with_Equipment.xlsx
+++ b/projects/dar-cairo-room-naming/Rooms_with_Equipment.xlsx
@@ -32821,12 +32821,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>entity:QNL_B-004_Analogue-Resources</t>
+          <t>entity:QNL_B-004_Analog-Resources</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B.004 ANALOGUE RESOURCES</t>
+          <t>B.004 ANALOG RESOURCES</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -33143,12 +33143,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>entity:QNL_B-021_Arabic-Sudies</t>
+          <t>entity:QNL_B-021_Arabic-Studies</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B.021 ARABIC SUDIES</t>
+          <t>B.021 ARABIC STUDIES</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -33281,12 +33281,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>entity:QNL_B-024_Ad-Collection</t>
+          <t>entity:QNL_B-024_Ad-Collections</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B.024 AD COLLECTION</t>
+          <t>B.024 AD COLLECTIONS</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -35075,12 +35075,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>entity:QNL_B-093_Transh-Chamber</t>
+          <t>entity:QNL_B-093_Trash-Chamber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>B.093 TRANSH CHAMBER</t>
+          <t>B.093 TRASH CHAMBER</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -35167,12 +35167,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>entity:QNL_B-101_Shipping-Clirk</t>
+          <t>entity:QNL_B-101_Shipping-Clerk</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>B.101 SHIPPING CLIRK</t>
+          <t>B.101 SHIPPING CLERK</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -35351,12 +35351,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>entity:QNL_B-105_Security-Contol-Room</t>
+          <t>entity:QNL_B-105_Security-Control-Room</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>B.105 SECURITY CONTOL ROOM</t>
+          <t>B.105 SECURITY CONTROL ROOM</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -36363,12 +36363,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>entity:QNL_B-207_Reserchers-Reading-Area</t>
+          <t>entity:QNL_B-207_Researchers-Reading-Area</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>B.207 RESERCHERS READING AREA</t>
+          <t>B.207 RESEARCHERS READING AREA</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -37973,12 +37973,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-080_Public-Services</t>
+          <t>entity:QNL_L1-080_Public-Service</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>L1.080 PUBLIC SERVICES</t>
+          <t>L1.080 PUBLIC SERVICE</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -39169,12 +39169,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-153_Furniture-Store</t>
+          <t>entity:QNL_L1-153_Furniture-Storage</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>L1.153 FURNITURE STORE</t>
+          <t>L1.153 FURNITURE STORAGE</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -40273,12 +40273,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>entity:QNL_L2-022_Academic-Pers-Libraria</t>
+          <t>entity:QNL_L2-022_Academic-Pers-Librarian</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>L2.022 ACADEMIC PERS LIBRARIA</t>
+          <t>L2.022 ACADEMIC PERS LIBRARIAN</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -40595,12 +40595,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>entity:QNL_L2-048_VIP-Wating</t>
+          <t>entity:QNL_L2-048_VIP-Waiting</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>L2.048 VIP WATING</t>
+          <t>L2.048 VIP WAITING</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -40687,12 +40687,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>entity:QNL_L2-070_Indivistudy-Room</t>
+          <t>entity:QNL_L2-070_Indivi-Study-Room</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>L2.070 INDIVISTUDY ROOM</t>
+          <t>L2.070 INDIVI STUDY ROOM</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -40733,12 +40733,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>entity:QNL_L2-073_Indivistudy-Room</t>
+          <t>entity:QNL_L2-073_Indivi-Study-Room</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>L2.073 INDIVISTUDY ROOM</t>
+          <t>L2.073 INDIVI STUDY ROOM</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -40871,12 +40871,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>entity:QNL_L2-087_Auditorium-High-Levlel-In-Ceiling-Void</t>
+          <t>entity:QNL_L2-087_Auditorium-High-Level-In-Ceiling-Void</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>L2.087 AUDITORIUM HIGH LEVLEL IN CEILING VOID</t>
+          <t>L2.087 AUDITORIUM HIGH LEVEL IN CEILING VOID</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">

--- a/projects/dar-cairo-room-naming/Rooms_with_Equipment.xlsx
+++ b/projects/dar-cairo-room-naming/Rooms_with_Equipment.xlsx
@@ -39721,12 +39721,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-E1_Shaft</t>
+          <t>entity:QNL_L1-E1_Elec-Shaft</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>E1 SHAFT</t>
+          <t>E1 ELEC SHAFT</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -39767,12 +39767,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>entity:QNL_L1-E2_Shaft</t>
+          <t>entity:QNL_L1-E2_Elec-Shaft</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>E2 SHAFT</t>
+          <t>E2 ELEC SHAFT</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
